--- a/simultaneous-refactor-clone-pairs/refactoring_special_samples.xlsx
+++ b/simultaneous-refactor-clone-pairs/refactoring_special_samples.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dreamxia/Downloads/find samples/type1-clone-pairs-simultaneous-extract-method-vscode/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dreamxia/Downloads/find samples/simultaneous-refactor-clone-pairs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D696C6D5-F082-8D49-8636-73677828A73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A77F9E-557D-F44E-83B6-1967C2A18B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3100" yWindow="2320" windowWidth="25080" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36300" yWindow="1580" windowWidth="25080" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="81">
   <si>
     <t>Sample N</t>
   </si>
@@ -583,6 +583,92 @@
   </si>
   <si>
     <t>Jruby: 427-1-2</t>
+  </si>
+  <si>
+    <t>private static void extracted(String name, byte[] bytes)</t>
+  </si>
+  <si>
+    <t>private void extracted(StaticScope scope)</t>
+  </si>
+  <si>
+    <t>private DynamicMethod extracted(String oldName, Ruby runtime, DynamicMethod method)</t>
+  </si>
+  <si>
+    <t>private static IRubyObject extracted(IRubyObject obj, RubyClass target, String convertMethod, boolean raise)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clone 1: 
+if (realmAccess instanceof Map) {
+            @SuppressWarnings("unchecked")
+            Map&lt;String, Object&gt; realmAccessMap = (Map&lt;String, Object&gt;) realmAccess;
+            Object realmRoles = realmAccessMap.get("roles");
+            if (realmRoles instanceof Collection) {
+                @SuppressWarnings("unchecked")
+                Collection&lt;String&gt; realmRolesCollection = (Collection&lt;String&gt;) realmRoles;
+                roles.addAll(realmRolesCollection);
+            }
+         }
+Clone 2: 
+if (clientAccess instanceof Map) {
+                @SuppressWarnings("unchecked")
+                Map&lt;String, Object&gt; clientAccessMap = (Map&lt;String, Object&gt;) clientAccess;
+                Object clientRoles = clientAccessMap.get("roles");
+                if (clientRoles instanceof Collection) {
+                    @SuppressWarnings("unchecked")
+                    Collection&lt;String&gt; clientRolesCollection = (Collection&lt;String&gt;) clientRoles;
+                    roles.addAll(clientRolesCollection);
+                }
+            }
+</t>
+  </si>
+  <si>
+    <t>private static void extracted(Set&lt;String&gt; roles, Object realmAccess)</t>
+  </si>
+  <si>
+    <t>private CamelCatalog getCatalog(String repos)</t>
+  </si>
+  <si>
+    <t>Extract signature</t>
+  </si>
+  <si>
+    <t>/home/user1-system11/research_dream/llm-clone/simultaneous-refactor-clone-pairs/html.reports/117-1-2.htm</t>
+  </si>
+  <si>
+    <t>/home/user1-system11/research_dream/llm-clone/simultaneous-refactor-clone-pairs/html.reports/364-1-2.htm</t>
+  </si>
+  <si>
+    <t>/home/user1-system11/research_dream/llm-clone/simultaneous-refactor-clone-pairs/html.reports/427-1-2.htm</t>
+  </si>
+  <si>
+    <t>/home/user1-system11/research_dream/llm-clone/simultaneous-refactor-clone-pairs/html.reports/661-1-2.htm</t>
+  </si>
+  <si>
+    <t>FilePath_before_refactor</t>
+  </si>
+  <si>
+    <t>FilePath_after_refactor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/home/user1-system11/research_dream/llm-clone/automate_extract_method_refactoring/data/CloneFile/camel_110_91_vs_camel_110_92/KeycloakSecurityHelper.java
+</t>
+  </si>
+  <si>
+    <t>/home/user1-system11/research_dream/llm-clone/simultaneous-refactor-clone-pairs/camel_2720_2658_vs_camel_2720_2660/ref1</t>
+  </si>
+  <si>
+    <t>/home/user1-system11/research_dream/llm-clone/simultaneous-refactor-clone-pairs/camel_110_91_vs_camel_110_92/ref1</t>
+  </si>
+  <si>
+    <t>/home/user1-system11/research_dream/llm-clone/simultaneous-refactor-clone-pairs/117-1-2/ref1</t>
+  </si>
+  <si>
+    <t>/home/user1-system11/research_dream/llm-clone/simultaneous-refactor-clone-pairs/364-1-2/ref1</t>
+  </si>
+  <si>
+    <t>/home/user1-system11/research_dream/llm-clone/simultaneous-refactor-clone-pairs/427-1-2/ref1</t>
+  </si>
+  <si>
+    <t>/home/user1-system11/research_dream/llm-clone/simultaneous-refactor-clone-pairs/661-1-2/ref1</t>
   </si>
 </sst>
 </file>
@@ -2119,20 +2205,22 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.1640625" style="1" customWidth="1"/>
-    <col min="2" max="3" width="32" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="89.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.33203125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.33203125" style="1"/>
+    <col min="2" max="2" width="28.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32" style="1" customWidth="1"/>
+    <col min="4" max="5" width="25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="1" customWidth="1"/>
+    <col min="7" max="7" width="89.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.25" customHeight="1">
+    <row r="1" spans="1:9" ht="20.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2143,19 +2231,25 @@
         <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="296" customHeight="1">
+    <row r="2" spans="1:9" ht="296" customHeight="1">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2166,19 +2260,25 @@
         <v>22</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="E2" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="G2" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="68" customHeight="1">
+    <row r="3" spans="1:9" ht="96" customHeight="1">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2191,17 +2291,23 @@
       <c r="D3" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="7">
+      <c r="H3" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="191" customHeight="1">
+    <row r="4" spans="1:9" ht="191" customHeight="1">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -2209,22 +2315,28 @@
         <v>46</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="D4" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="7">
+      <c r="H4" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="191" customHeight="1">
+    <row r="5" spans="1:9" ht="191" customHeight="1">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2232,22 +2344,28 @@
         <v>52</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D5" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="G5" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="7">
+      <c r="H5" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="191" customHeight="1">
+    <row r="6" spans="1:9" ht="191" customHeight="1">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2255,22 +2373,28 @@
         <v>59</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D6" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="7">
+      <c r="H6" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="112" customHeight="1">
+    <row r="7" spans="1:9" ht="112" customHeight="1">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2278,27 +2402,30 @@
         <v>42</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D7" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="G7" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="7">
+      <c r="H7" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="7">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" xr:uid="{CAA5EAA3-2BBB-E54E-8CD6-A884B6E6160D}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{E0D2752C-1669-7440-89B7-59F5223565B9}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{0D926B7E-DDE2-504F-88A0-75A55B63C1B9}"/>
-    <hyperlink ref="C6" r:id="rId4" xr:uid="{72BF7728-34E4-9345-BA09-D4609B5D7885}"/>
+    <hyperlink ref="C6" r:id="rId1" display="file:///Users/dreamxia/Downloads/find%20samples/jruby-1.4.0-nicad/html.reports/427-1-2.htm" xr:uid="{72BF7728-34E4-9345-BA09-D4609B5D7885}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
